--- a/Ifeyefunmi2016.xlsx
+++ b/Ifeyefunmi2016.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohd Shahrom Ismail\Desktop\Cylinder - Loading imperfection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EBBF2E-621E-4DB3-84A9-92C49C41F111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6290E945-FEB6-4F92-8BD0-3E706D7A78DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{2220B5AF-4434-4E44-B023-2C724A42ECF9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2220B5AF-4434-4E44-B023-2C724A42ECF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Validation" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="175">
   <si>
     <t>Cylinder</t>
   </si>
@@ -590,6 +590,30 @@
   <si>
     <t>a</t>
   </si>
+  <si>
+    <t>Ry​ (External Pressure)</t>
+  </si>
+  <si>
+    <t>ECCS Linear (m=1,n=1)</t>
+  </si>
+  <si>
+    <t>Das Parabolic (m=1,n=2)</t>
+  </si>
+  <si>
+    <t>DNV Quadratic (m=2,n=2)</t>
+  </si>
+  <si>
+    <t>Excel Formula:</t>
+  </si>
+  <si>
+    <t>1 - Ry_cell</t>
+  </si>
+  <si>
+    <t>1 - (Ry_cell^2)</t>
+  </si>
+  <si>
+    <t>SQRT(1 - (Ry_cell^2))</t>
+  </si>
 </sst>
 </file>
 
@@ -598,7 +622,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,6 +709,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -782,7 +812,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -934,11 +964,11 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,6 +978,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7491,6 +7527,436 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A-ST</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$7:$H$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74797210010314752</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$6:$H$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0993357122227088</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1635315637626205</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1221960316646946</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-620D-468B-907A-602DDFC10D49}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$C$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ASME</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$13:$H$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10996449923390449</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21992899846780897</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3298934977017135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43985800903740052</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$12:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.87615886565374113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88419529253196438</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.85167966360143976</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79981614849735561</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F5A5-482F-90F7-17B84367F704}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$D$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Case 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$19:$H$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5403527043672458E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13080705408734492</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19621058113101736</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26161410817468983</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$18:$H$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99251861030624322</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0243944856971605</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0502206528591704</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0696617070239347</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-952A-44F7-8C44-9446FD758213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Case 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$25:$H$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5190847912514907E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13038169582502981</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19557254373754471</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26076339165005963</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$24:$H$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.98453721905968661</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0240435529302887</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0496864897095952</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0690747486793439</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-952A-44F7-8C44-9446FD758213}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AI$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ECCS Linear (m=1,n=1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AI$49:$AI$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A3AE-401B-B205-0449D75CAA93}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1155444592"/>
+        <c:axId val="1155441712"/>
+      </c:scatterChart>
+      <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -7575,112 +8041,16 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1155444592"/>
-        <c:axId val="1155441712"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Combine load'!$C$3</c:f>
+              <c:f>'Combine load'!$AJ$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>A-ST</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$7:$H$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.74797210010314752</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$6:$H$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0993357122227088</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.1635315637626205</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.1221960316646946</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-620D-468B-907A-602DDFC10D49}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Combine load'!$C$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ASME</c:v>
+                  <c:v>Das Parabolic (m=1,n=2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7700,69 +8070,75 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$13:$H$13</c:f>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.10996449923390449</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21992899846780897</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3298934977017135</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.43985800903740052</c:v>
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$12:$H$12</c:f>
+              <c:f>'Combine load'!$AJ$49:$AJ$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.87615886565374113</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88419529253196438</c:v>
+                  <c:v>0.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.85167966360143976</c:v>
+                  <c:v>0.84</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.79981614849735561</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F5A5-482F-90F7-17B84367F704}"/>
+              <c16:uniqueId val="{00000001-A3AE-401B-B205-0449D75CAA93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Combine load'!$D$15</c:f>
+              <c:f>'Combine load'!$AK$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Case 1</c:v>
+                  <c:v>DNV Quadratic (m=2,n=2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7772,7 +8148,7 @@
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
+              <a:prstDash val="lgDash"/>
               <a:miter lim="800000"/>
             </a:ln>
             <a:effectLst/>
@@ -7782,138 +8158,62 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$19:$H$19</c:f>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5403527043672458E-2</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13080705408734492</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.19621058113101736</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.26161410817468983</c:v>
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$18:$H$18</c:f>
+              <c:f>'Combine load'!$AK$49:$AK$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.99251861030624322</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0243944856971605</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0502206528591704</c:v>
+                  <c:v>0.91700000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0696617070239347</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-952A-44F7-8C44-9446FD758213}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Combine load'!$D$21</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Case 2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$25:$H$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.5190847912514907E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13038169582502981</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.19557254373754471</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.26076339165005963</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$24:$H$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.98453721905968661</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0240435529302887</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.0496864897095952</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0690747486793439</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-952A-44F7-8C44-9446FD758213}"/>
+              <c16:uniqueId val="{00000002-A3AE-401B-B205-0449D75CAA93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10158,6 +10458,430 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$C$58</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ASME</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$62:$H$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.19165074045954744</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38330148091909488</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57495222137864233</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76660298292968387</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$61:$H$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.72839772534174407</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73507883682442632</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.70804685543440926</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.66492994146943474</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A390-4A99-896C-2E6DBC5FC5EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$D$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Case 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$68:$H$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13457012330811319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26914024661622638</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40371036992433962</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.53828049323245275</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$67:$H$67</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.64021129869693971</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.65986951324360532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67323059287047626</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49315680356502001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A390-4A99-896C-2E6DBC5FC5EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$D$70</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Case 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$74:$G$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13417458613678213</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26834917227356425</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5366983445471285</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$73:$G$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.63659154340479041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.62226743330433054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56492968328432114</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A390-4A99-896C-2E6DBC5FC5EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$D$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Case 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$80:$H$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10356245254862947</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20712490509725895</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3106873576458884</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4142498101945179</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$D$79:$H$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.64689054758480724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.62734335263697361</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63631528533327819</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48179924041939587</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A390-4A99-896C-2E6DBC5FC5EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AI$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ECCS Linear (m=1,n=1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AI$49:$AI$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D2E1-42CF-B0FA-32B125F1D23E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="103608592"/>
+        <c:axId val="103632592"/>
+      </c:scatterChart>
+      <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -10236,30 +10960,16 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="103608592"/>
-        <c:axId val="103632592"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Combine load'!$C$58</c:f>
+              <c:f>'Combine load'!$AJ$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ASME</c:v>
+                  <c:v>Das Parabolic (m=1,n=2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10269,7 +10979,7 @@
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
+              <a:prstDash val="lgDash"/>
               <a:miter lim="800000"/>
             </a:ln>
             <a:effectLst/>
@@ -10279,69 +10989,75 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$62:$H$62</c:f>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.19165074045954744</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.38330148091909488</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.57495222137864233</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.76660298292968387</c:v>
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$61:$H$61</c:f>
+              <c:f>'Combine load'!$AJ$49:$AJ$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.72839772534174407</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.73507883682442632</c:v>
+                  <c:v>0.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.70804685543440926</c:v>
+                  <c:v>0.84</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.66492994146943474</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A390-4A99-896C-2E6DBC5FC5EF}"/>
+              <c16:uniqueId val="{00000001-D2E1-42CF-B0FA-32B125F1D23E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="7"/>
+          <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Combine load'!$D$64</c:f>
+              <c:f>'Combine load'!$AK$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Case 1</c:v>
+                  <c:v>DNV Quadratic (m=2,n=2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10351,7 +11067,7 @@
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
+              <a:prstDash val="lgDash"/>
               <a:miter lim="800000"/>
             </a:ln>
             <a:effectLst/>
@@ -10361,214 +11077,62 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$68:$H$68</c:f>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13457012330811319</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.26914024661622638</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.40371036992433962</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.53828049323245275</c:v>
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Combine load'!$D$67:$H$67</c:f>
+              <c:f>'Combine load'!$AK$49:$AK$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.64021129869693971</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.65986951324360532</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.67323059287047626</c:v>
+                  <c:v>0.91700000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.49315680356502001</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A390-4A99-896C-2E6DBC5FC5EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Combine load'!$D$70</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Case 2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$74:$G$74</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13417458613678213</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.26834917227356425</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.5366983445471285</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$73:$G$73</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.63659154340479041</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.62226743330433054</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.56492968328432114</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A390-4A99-896C-2E6DBC5FC5EF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Combine load'!$D$76</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Case 3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$80:$H$80</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.10356245254862947</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.20712490509725895</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.3106873576458884</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.4142498101945179</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Combine load'!$D$79:$H$79</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.64689054758480724</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.62734335263697361</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.63631528533327819</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.48179924041939587</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A390-4A99-896C-2E6DBC5FC5EF}"/>
+              <c16:uniqueId val="{00000002-D2E1-42CF-B0FA-32B125F1D23E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11195,6 +11759,270 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-2C55-46B6-A97C-C670D6B7C987}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AI$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ECCS Linear (m=1,n=1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AI$49:$AI$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C439-48D7-A9F0-3E2A6FCFA759}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AJ$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Das Parabolic (m=1,n=2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AJ$49:$AJ$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C439-48D7-A9F0-3E2A6FCFA759}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AK$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DNV Quadratic (m=2,n=2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AK$49:$AK$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C439-48D7-A9F0-3E2A6FCFA759}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11852,6 +12680,270 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-B84F-42F6-BC3F-A98184C7D07C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AI$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ECCS Linear (m=1,n=1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AI$49:$AI$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-91B9-4FE4-B703-ACCC6F9E43C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AJ$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Das Parabolic (m=1,n=2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AJ$49:$AJ$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-91B9-4FE4-B703-ACCC6F9E43C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Combine load'!$AK$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DNV Quadratic (m=2,n=2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDash"/>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AK$49:$AK$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Combine load'!$AH$49:$AH$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-91B9-4FE4-B703-ACCC6F9E43C8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -24946,7 +26038,9 @@
     <col min="44" max="45" width="14.08984375" style="1" customWidth="1"/>
     <col min="46" max="46" width="15.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="28.81640625" style="1" customWidth="1"/>
-    <col min="48" max="16384" width="8.7265625" style="1"/>
+    <col min="48" max="50" width="8.7265625" style="1"/>
+    <col min="51" max="51" width="8.7265625" style="1" customWidth="1"/>
+    <col min="52" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:47" ht="28">
@@ -27387,7 +28481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="11:39" ht="50">
+    <row r="47" spans="11:39" ht="70">
       <c r="K47" s="2" t="s">
         <v>8</v>
       </c>
@@ -27406,8 +28500,20 @@
       <c r="R47" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="AH47" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI47" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ47" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK47" s="34" t="s">
+        <v>170</v>
+      </c>
     </row>
-    <row r="48" spans="11:39">
+    <row r="48" spans="11:39" ht="28">
       <c r="K48" s="3">
         <v>0</v>
       </c>
@@ -27426,8 +28532,20 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
+      <c r="AH48" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI48" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ48" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK48" s="55" t="s">
+        <v>174</v>
+      </c>
     </row>
-    <row r="49" spans="3:18">
+    <row r="49" spans="3:37">
       <c r="K49" s="3">
         <v>16.387499999999999</v>
       </c>
@@ -27446,8 +28564,20 @@
       <c r="R49" s="3">
         <v>9.9483799999999997E-3</v>
       </c>
+      <c r="AH49" s="61">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="34">
+        <v>1</v>
+      </c>
+      <c r="AJ49" s="34">
+        <v>1</v>
+      </c>
+      <c r="AK49" s="34">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="3:18">
+    <row r="50" spans="3:37">
       <c r="K50" s="3">
         <v>32.568599999999996</v>
       </c>
@@ -27466,8 +28596,20 @@
       <c r="R50" s="3">
         <v>1.97845E-2</v>
       </c>
+      <c r="AH50" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="AI50" s="34">
+        <v>0.8</v>
+      </c>
+      <c r="AJ50" s="34">
+        <v>0.96</v>
+      </c>
+      <c r="AK50" s="34">
+        <v>0.98</v>
+      </c>
     </row>
-    <row r="51" spans="3:18">
+    <row r="51" spans="3:37">
       <c r="C51" s="11" t="s">
         <v>1</v>
       </c>
@@ -27496,8 +28638,20 @@
       <c r="R51" s="3">
         <v>3.4297800000000003E-2</v>
       </c>
+      <c r="AH51" s="34">
+        <v>0.4</v>
+      </c>
+      <c r="AI51" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="AJ51" s="34">
+        <v>0.84</v>
+      </c>
+      <c r="AK51" s="34">
+        <v>0.91700000000000004</v>
+      </c>
     </row>
-    <row r="52" spans="3:18">
+    <row r="52" spans="3:37">
       <c r="C52" s="8" t="s">
         <v>33</v>
       </c>
@@ -27524,8 +28678,20 @@
       <c r="R52" s="3">
         <v>5.5368199999999999E-2</v>
       </c>
+      <c r="AH52" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="AI52" s="34">
+        <v>0.4</v>
+      </c>
+      <c r="AJ52" s="34">
+        <v>0.64</v>
+      </c>
+      <c r="AK52" s="34">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="53" spans="3:18">
+    <row r="53" spans="3:37">
       <c r="C53" s="13" t="s">
         <v>22</v>
       </c>
@@ -27559,8 +28725,20 @@
       <c r="R53" s="5">
         <v>8.4786E-2</v>
       </c>
+      <c r="AH53" s="34">
+        <v>0.8</v>
+      </c>
+      <c r="AI53" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="AJ53" s="34">
+        <v>0.36</v>
+      </c>
+      <c r="AK53" s="34">
+        <v>0.6</v>
+      </c>
     </row>
-    <row r="54" spans="3:18">
+    <row r="54" spans="3:37">
       <c r="C54" s="13" t="s">
         <v>23</v>
       </c>
@@ -27596,8 +28774,20 @@
       <c r="R54" s="3">
         <v>9.9621199999999993E-2</v>
       </c>
+      <c r="AH54" s="34">
+        <v>1</v>
+      </c>
+      <c r="AI54" s="34">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="34">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="34">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="3:18">
+    <row r="55" spans="3:37">
       <c r="C55" s="13" t="s">
         <v>38</v>
       </c>
@@ -27636,7 +28826,7 @@
         <v>0.113757</v>
       </c>
     </row>
-    <row r="56" spans="3:18">
+    <row r="56" spans="3:37">
       <c r="C56" s="13" t="s">
         <v>39</v>
       </c>
@@ -27675,7 +28865,7 @@
         <v>0.132548</v>
       </c>
     </row>
-    <row r="57" spans="3:18">
+    <row r="57" spans="3:37">
       <c r="K57" s="3">
         <v>149.916</v>
       </c>
@@ -27695,7 +28885,7 @@
         <v>0.16559599999999999</v>
       </c>
     </row>
-    <row r="58" spans="3:18">
+    <row r="58" spans="3:37">
       <c r="C58" s="8" t="s">
         <v>40</v>
       </c>
@@ -27723,7 +28913,7 @@
         <v>0.22952900000000001</v>
       </c>
     </row>
-    <row r="59" spans="3:18">
+    <row r="59" spans="3:37">
       <c r="C59" s="13" t="s">
         <v>22</v>
       </c>
@@ -27761,7 +28951,7 @@
         <v>0.271171</v>
       </c>
     </row>
-    <row r="60" spans="3:18">
+    <row r="60" spans="3:37">
       <c r="C60" s="13" t="s">
         <v>23</v>
       </c>
@@ -27799,7 +28989,7 @@
         <v>0.34204600000000002</v>
       </c>
     </row>
-    <row r="61" spans="3:18">
+    <row r="61" spans="3:37">
       <c r="C61" s="13" t="s">
         <v>38</v>
       </c>
@@ -27842,7 +29032,7 @@
         <v>0.46204600000000001</v>
       </c>
     </row>
-    <row r="62" spans="3:18">
+    <row r="62" spans="3:37">
       <c r="C62" s="13" t="s">
         <v>39</v>
       </c>
@@ -27885,7 +29075,7 @@
         <v>0.49326500000000001</v>
       </c>
     </row>
-    <row r="63" spans="3:18">
+    <row r="63" spans="3:37">
       <c r="K63" s="3">
         <v>149.26599999999999</v>
       </c>
@@ -27905,7 +29095,7 @@
         <v>0.52530200000000005</v>
       </c>
     </row>
-    <row r="64" spans="3:18">
+    <row r="64" spans="3:37">
       <c r="C64" s="8" t="s">
         <v>33</v>
       </c>
@@ -28628,14 +29818,14 @@
       </c>
     </row>
     <row r="2" spans="2:20">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="55"/>
+      <c r="E2" s="56"/>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
@@ -30669,19 +31859,19 @@
       <c r="B20" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="60" t="s">
         <v>130</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="60" t="s">
         <v>133</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="56" t="s">
+      <c r="G20" s="60" t="s">
         <v>136</v>
       </c>
       <c r="R20" s="20">
@@ -30712,11 +31902,11 @@
     </row>
     <row r="21" spans="2:30" ht="14.5">
       <c r="B21" s="59"/>
-      <c r="C21" s="56"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="37"/>
-      <c r="E21" s="56"/>
+      <c r="E21" s="60"/>
       <c r="F21" s="37"/>
-      <c r="G21" s="56"/>
+      <c r="G21" s="60"/>
       <c r="I21" s="17" t="s">
         <v>45</v>
       </c>
@@ -30752,15 +31942,15 @@
     </row>
     <row r="22" spans="2:30">
       <c r="B22" s="59"/>
-      <c r="C22" s="56"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="56"/>
+      <c r="E22" s="60"/>
       <c r="F22" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="56"/>
+      <c r="G22" s="60"/>
       <c r="R22" s="20">
         <v>0.89715199999999995</v>
       </c>
@@ -30789,11 +31979,11 @@
     </row>
     <row r="23" spans="2:30" ht="14.5">
       <c r="B23" s="59"/>
-      <c r="C23" s="56"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="37"/>
-      <c r="E23" s="56"/>
+      <c r="E23" s="60"/>
       <c r="F23" s="37"/>
-      <c r="G23" s="56"/>
+      <c r="G23" s="60"/>
       <c r="R23" s="20">
         <v>0.94735599999999998</v>
       </c>
@@ -30822,13 +32012,13 @@
     </row>
     <row r="24" spans="2:30" ht="14.5">
       <c r="B24" s="59"/>
-      <c r="C24" s="56"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="37"/>
-      <c r="E24" s="56"/>
+      <c r="E24" s="60"/>
       <c r="F24" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="56"/>
+      <c r="G24" s="60"/>
       <c r="R24" s="20">
         <v>0.996452</v>
       </c>
@@ -30859,19 +32049,19 @@
       <c r="B25" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="60" t="s">
         <v>137</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="60" t="s">
         <v>133</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="G25" s="56" t="s">
+      <c r="G25" s="60" t="s">
         <v>136</v>
       </c>
       <c r="R25" s="20">
@@ -30902,11 +32092,11 @@
     </row>
     <row r="26" spans="2:30" ht="14.5">
       <c r="B26" s="59"/>
-      <c r="C26" s="56"/>
+      <c r="C26" s="60"/>
       <c r="D26" s="37"/>
-      <c r="E26" s="56"/>
+      <c r="E26" s="60"/>
       <c r="F26" s="37"/>
-      <c r="G26" s="56"/>
+      <c r="G26" s="60"/>
       <c r="R26" s="20">
         <v>1.0581799999999999</v>
       </c>
@@ -30935,15 +32125,15 @@
     </row>
     <row r="27" spans="2:30">
       <c r="B27" s="59"/>
-      <c r="C27" s="56"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="56"/>
+      <c r="E27" s="60"/>
       <c r="F27" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="56"/>
+      <c r="G27" s="60"/>
       <c r="R27" s="20">
         <v>1.0783100000000001</v>
       </c>
@@ -30972,11 +32162,11 @@
     </row>
     <row r="28" spans="2:30" ht="14.5">
       <c r="B28" s="59"/>
-      <c r="C28" s="56"/>
+      <c r="C28" s="60"/>
       <c r="D28" s="37"/>
-      <c r="E28" s="56"/>
+      <c r="E28" s="60"/>
       <c r="F28" s="37"/>
-      <c r="G28" s="56"/>
+      <c r="G28" s="60"/>
       <c r="R28" s="20">
         <v>1.1148100000000001</v>
       </c>
@@ -31005,13 +32195,13 @@
     </row>
     <row r="29" spans="2:30" ht="14.5">
       <c r="B29" s="59"/>
-      <c r="C29" s="56"/>
+      <c r="C29" s="60"/>
       <c r="D29" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="56"/>
+      <c r="E29" s="60"/>
       <c r="F29" s="37"/>
-      <c r="G29" s="56"/>
+      <c r="G29" s="60"/>
       <c r="R29" s="20">
         <v>1.17547</v>
       </c>
@@ -31042,7 +32232,7 @@
       <c r="B30" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="60" t="s">
         <v>84</v>
       </c>
       <c r="D30" s="28" t="s">
@@ -31054,7 +32244,7 @@
       <c r="F30" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="G30" s="56" t="s">
+      <c r="G30" s="60" t="s">
         <v>136</v>
       </c>
       <c r="R30" s="20">
@@ -31085,11 +32275,11 @@
     </row>
     <row r="31" spans="2:30" ht="14.5">
       <c r="B31" s="59"/>
-      <c r="C31" s="56"/>
+      <c r="C31" s="60"/>
       <c r="D31" s="37"/>
       <c r="E31" s="37"/>
       <c r="F31" s="37"/>
-      <c r="G31" s="56"/>
+      <c r="G31" s="60"/>
       <c r="R31" s="20">
         <v>1.30958</v>
       </c>
@@ -31118,7 +32308,7 @@
     </row>
     <row r="32" spans="2:30">
       <c r="B32" s="59"/>
-      <c r="C32" s="56"/>
+      <c r="C32" s="60"/>
       <c r="D32" s="29" t="s">
         <v>138</v>
       </c>
@@ -31128,7 +32318,7 @@
       <c r="F32" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="G32" s="56"/>
+      <c r="G32" s="60"/>
       <c r="R32" s="20">
         <v>1.3811</v>
       </c>
@@ -31157,11 +32347,11 @@
     </row>
     <row r="33" spans="2:40" ht="14.5">
       <c r="B33" s="59"/>
-      <c r="C33" s="56"/>
+      <c r="C33" s="60"/>
       <c r="D33" s="37"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
-      <c r="G33" s="56"/>
+      <c r="G33" s="60"/>
       <c r="R33" s="20">
         <v>1.49068</v>
       </c>
@@ -31190,13 +32380,13 @@
     </row>
     <row r="34" spans="2:40" ht="14.5">
       <c r="B34" s="59"/>
-      <c r="C34" s="56"/>
+      <c r="C34" s="60"/>
       <c r="D34" s="37"/>
       <c r="E34" s="38" t="s">
         <v>41</v>
       </c>
       <c r="F34" s="37"/>
-      <c r="G34" s="56"/>
+      <c r="G34" s="60"/>
       <c r="R34" s="20">
         <v>1.6021000000000001</v>
       </c>
@@ -31227,7 +32417,7 @@
       <c r="B35" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="60" t="s">
         <v>88</v>
       </c>
       <c r="D35" s="28" t="s">
@@ -31239,7 +32429,7 @@
       <c r="F35" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="56" t="s">
+      <c r="G35" s="60" t="s">
         <v>136</v>
       </c>
       <c r="R35" s="20">
@@ -31270,15 +32460,15 @@
     </row>
     <row r="36" spans="2:40" ht="14.5">
       <c r="B36" s="59"/>
-      <c r="C36" s="56"/>
+      <c r="C36" s="60"/>
       <c r="D36" s="37"/>
       <c r="E36" s="37"/>
       <c r="F36" s="37"/>
-      <c r="G36" s="56"/>
+      <c r="G36" s="60"/>
     </row>
     <row r="37" spans="2:40">
       <c r="B37" s="59"/>
-      <c r="C37" s="56"/>
+      <c r="C37" s="60"/>
       <c r="D37" s="29" t="s">
         <v>139</v>
       </c>
@@ -31288,15 +32478,15 @@
       <c r="F37" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="G37" s="56"/>
+      <c r="G37" s="60"/>
     </row>
     <row r="38" spans="2:40" ht="28.5">
       <c r="B38" s="59"/>
-      <c r="C38" s="56"/>
+      <c r="C38" s="60"/>
       <c r="D38" s="37"/>
       <c r="E38" s="37"/>
       <c r="F38" s="37"/>
-      <c r="G38" s="56"/>
+      <c r="G38" s="60"/>
       <c r="AL38" s="17"/>
       <c r="AM38" s="19" t="s">
         <v>146</v>
@@ -31307,7 +32497,7 @@
     </row>
     <row r="39" spans="2:40" ht="14.5">
       <c r="B39" s="59"/>
-      <c r="C39" s="56"/>
+      <c r="C39" s="60"/>
       <c r="D39" s="38" t="s">
         <v>140</v>
       </c>
@@ -31315,7 +32505,7 @@
       <c r="F39" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="G39" s="56"/>
+      <c r="G39" s="60"/>
       <c r="AL39" s="20" t="s">
         <v>144</v>
       </c>
@@ -31388,6 +32578,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C30:C34"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="U3:V3"/>
     <mergeCell ref="B35:B39"/>
     <mergeCell ref="C35:C39"/>
     <mergeCell ref="G35:G39"/>
@@ -31400,12 +32596,6 @@
     <mergeCell ref="E25:E29"/>
     <mergeCell ref="G25:G29"/>
     <mergeCell ref="B30:B34"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="U3:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
